--- a/Documentation/GMEPay+_WBS.xlsx
+++ b/Documentation/GMEPay+_WBS.xlsx
@@ -1421,7 +1421,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Entity model</t>
+          <t>Entity model; + Partner.settlement_rounding_mode field</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Txn schema</t>
+          <t>Txn schema; + locked booked_settlement_amount &amp; rounding_mode &amp; residual</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Commit logic</t>
+          <t>Commit logic; + book settlement under partner rule, lock on txn, post residual</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>Revenue capture</t>
+          <t>Revenue capture; + rounding-residual posting to REVENUE_ROUNDING</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="K71" s="8" t="inlineStr">
         <is>
-          <t>Partner UI</t>
+          <t>Partner UI; + settlement-rounding-mode setting on partner</t>
         </is>
       </c>
       <c r="L71" s="8" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>Vector results</t>
+          <t>Vector results; + rounding-residual reconciliation tests</t>
         </is>
       </c>
       <c r="L112" s="4" t="inlineStr">

--- a/Documentation/GMEPay+_WBS.xlsx
+++ b/Documentation/GMEPay+_WBS.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phases &amp; Milestones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completion Plan v3" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phases &amp; Milestones" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS'!$A$1:$L$125</definedName>
@@ -25,7 +26,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,8 +67,39 @@
       <color rgb="002E75B6"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00BF8F00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -87,6 +119,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE9E7"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -201,6 +238,49 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -567,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L126"/>
+  <dimension ref="A1:S145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -582,6 +662,13 @@
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -645,6 +732,41 @@
           <t>Primary Role</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Tickets</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>% Done</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Status (audit 2026-06-10)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Completion Phase (v3)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -701,6 +823,33 @@
           <t>PM</t>
         </is>
       </c>
+      <c r="M2" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="N2" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R2" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S2" s="35" t="inlineStr">
+        <is>
+          <t>R0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -757,6 +906,33 @@
           <t>BA</t>
         </is>
       </c>
+      <c r="M3" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="N3" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q3" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R3" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S3" s="35" t="inlineStr">
+        <is>
+          <t>R0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -813,6 +989,33 @@
           <t>PM</t>
         </is>
       </c>
+      <c r="M4" s="35" t="n">
+        <v>33</v>
+      </c>
+      <c r="N4" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="35" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="R4" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S4" s="35" t="inlineStr">
+        <is>
+          <t>R0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -869,6 +1072,33 @@
           <t>ARCH</t>
         </is>
       </c>
+      <c r="M5" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="N5" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R5" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S5" s="35" t="inlineStr">
+        <is>
+          <t>R0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -925,6 +1155,33 @@
           <t>PM</t>
         </is>
       </c>
+      <c r="M6" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="N6" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q6" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R6" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S6" s="35" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -981,6 +1238,33 @@
           <t>BA</t>
         </is>
       </c>
+      <c r="M7" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="N7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q7" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R7" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S7" s="35" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1037,6 +1321,33 @@
           <t>ARCH</t>
         </is>
       </c>
+      <c r="M8" s="35" t="n">
+        <v>33</v>
+      </c>
+      <c r="N8" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="P8" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q8" s="35" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="R8" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S8" s="35" t="inlineStr">
+        <is>
+          <t>R0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1093,6 +1404,33 @@
           <t>ARCH</t>
         </is>
       </c>
+      <c r="M9" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="N9" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="P9" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="35" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="R9" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S9" s="35" t="inlineStr">
+        <is>
+          <t>R0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1149,6 +1487,33 @@
           <t>ARCH</t>
         </is>
       </c>
+      <c r="M10" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="N10" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R10" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S10" s="35" t="inlineStr">
+        <is>
+          <t>R0</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1205,6 +1570,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M11" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="N11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="P11" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q11" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R11" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S11" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1261,6 +1653,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M12" s="35" t="n">
+        <v>33</v>
+      </c>
+      <c r="N12" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q12" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R12" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S12" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1317,6 +1736,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M13" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="N13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q13" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R13" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S13" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1373,6 +1819,33 @@
           <t>DBA</t>
         </is>
       </c>
+      <c r="M14" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="N14" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="P14" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q14" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R14" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S14" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1429,6 +1902,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M15" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="N15" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="P15" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q15" s="35" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="R15" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S15" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1485,6 +1985,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M16" s="35" t="n">
+        <v>21</v>
+      </c>
+      <c r="N16" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P16" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q16" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R16" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S16" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1541,6 +2068,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M17" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="N17" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q17" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R17" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S17" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1597,6 +2151,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M18" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="N18" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="P18" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q18" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R18" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S18" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1653,6 +2234,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M19" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="N19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q19" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R19" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S19" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1709,6 +2317,33 @@
           <t>DBA</t>
         </is>
       </c>
+      <c r="M20" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="N20" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="P20" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q20" s="35" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="R20" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S20" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1765,6 +2400,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M21" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="N21" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q21" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R21" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S21" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1821,6 +2483,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M22" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="N22" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="P22" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R22" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S22" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -1877,6 +2566,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M23" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="N23" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R23" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S23" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1933,6 +2649,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M24" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="N24" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P24" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q24" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R24" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S24" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -1989,6 +2732,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M25" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="N25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q25" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R25" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S25" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -2045,6 +2815,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M26" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="N26" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q26" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R26" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S26" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -2101,6 +2898,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M27" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="N27" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q27" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R27" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S27" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -2157,6 +2981,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M28" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="N28" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P28" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q28" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R28" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S28" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -2213,6 +3064,33 @@
           <t>QA</t>
         </is>
       </c>
+      <c r="M29" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="N29" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P29" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q29" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R29" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S29" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2269,6 +3147,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M30" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="N30" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="P30" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q30" s="35" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="R30" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S30" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2325,6 +3230,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M31" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="N31" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="P31" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q31" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R31" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S31" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2381,6 +3313,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M32" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="N32" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P32" s="35" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q32" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R32" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S32" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2437,6 +3396,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M33" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="N33" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="O33" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q33" s="35" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="R33" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S33" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2493,6 +3479,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M34" s="35" t="n">
+        <v>36</v>
+      </c>
+      <c r="N34" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P34" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q34" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R34" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S34" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2549,6 +3562,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M35" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="N35" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P35" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q35" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R35" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S35" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2605,6 +3645,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M36" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="N36" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q36" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R36" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S36" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2661,6 +3728,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M37" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="N37" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q37" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R37" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S37" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -2717,6 +3811,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M38" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="N38" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="P38" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q38" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R38" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S38" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -2773,6 +3894,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M39" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="N39" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="P39" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q39" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R39" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S39" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -2829,6 +3977,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M40" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="N40" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="P40" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q40" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R40" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S40" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -2885,6 +4060,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M41" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="N41" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q41" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R41" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S41" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -2941,6 +4143,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M42" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="N42" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q42" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R42" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S42" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2997,6 +4226,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M43" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="N43" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="O43" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="P43" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q43" s="35" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="R43" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S43" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3053,6 +4309,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M44" s="35" t="n">
+        <v>19</v>
+      </c>
+      <c r="N44" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O44" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q44" s="35" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="R44" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S44" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3109,6 +4392,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M45" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="N45" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="P45" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q45" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R45" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S45" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3165,6 +4475,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M46" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="N46" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P46" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q46" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R46" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S46" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3221,6 +4558,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M47" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="N47" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q47" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R47" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S47" s="35" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3277,6 +4641,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M48" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="N48" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q48" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R48" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S48" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -3333,6 +4724,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M49" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="N49" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="O49" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="P49" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q49" s="35" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="R49" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S49" s="35" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -3389,6 +4807,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M50" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="N50" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="P50" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q50" s="35" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="R50" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S50" s="35" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -3445,6 +4890,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M51" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R51" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S51" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -3501,6 +4973,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M52" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="N52" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="P52" s="35" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q52" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R52" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S52" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -3557,6 +5056,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M53" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="N53" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="P53" s="35" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q53" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R53" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S53" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -3613,6 +5139,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M54" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="N54" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="P54" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q54" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R54" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S54" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -3669,6 +5222,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M55" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="N55" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="O55" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="P55" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q55" s="35" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="R55" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S55" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -3725,6 +5305,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M56" s="35" t="n">
+        <v>21</v>
+      </c>
+      <c r="N56" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="35" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q56" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R56" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S56" s="35" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -3781,6 +5388,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M57" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="N57" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="P57" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q57" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R57" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S57" s="35" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -3837,6 +5471,33 @@
           <t>BA</t>
         </is>
       </c>
+      <c r="M58" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="N58" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="P58" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q58" s="35" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="R58" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S58" s="35" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3893,6 +5554,33 @@
           <t>ARCH</t>
         </is>
       </c>
+      <c r="M59" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="N59" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="P59" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q59" s="35" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="R59" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S59" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3949,6 +5637,33 @@
           <t>DevOps</t>
         </is>
       </c>
+      <c r="M60" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="N60" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P60" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q60" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R60" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S60" s="35" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4005,6 +5720,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M61" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="N61" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P61" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q61" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R61" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S61" s="35" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4061,6 +5803,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M62" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="N62" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P62" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q62" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R62" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S62" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4117,6 +5886,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M63" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="N63" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q63" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R63" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S63" s="35" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4173,6 +5969,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M64" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="N64" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P64" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q64" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R64" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S64" s="35" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4229,6 +6052,33 @@
           <t>DevOps</t>
         </is>
       </c>
+      <c r="M65" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="N65" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q65" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R65" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S65" s="35" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4285,6 +6135,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M66" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="N66" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P66" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q66" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R66" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S66" s="35" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4341,6 +6218,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M67" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="N67" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="P67" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q67" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R67" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S67" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4397,6 +6301,33 @@
           <t>QA</t>
         </is>
       </c>
+      <c r="M68" s="35" t="n">
+        <v>36</v>
+      </c>
+      <c r="N68" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R68" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S68" s="35" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -4453,6 +6384,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M69" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="N69" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="P69" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R69" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S69" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -4509,6 +6467,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M70" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="N70" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R70" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S70" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -4565,6 +6550,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M71" s="35" t="n">
+        <v>37</v>
+      </c>
+      <c r="N71" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P71" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R71" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S71" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -4621,6 +6633,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M72" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="N72" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R72" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S72" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -4677,6 +6716,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M73" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="N73" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R73" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S73" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -4733,6 +6799,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M74" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="N74" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P74" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R74" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S74" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -4789,6 +6882,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M75" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="N75" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q75" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R75" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S75" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -4845,6 +6965,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M76" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="N76" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R76" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S76" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -4901,6 +7048,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M77" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="N77" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P77" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R77" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S77" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -4957,6 +7131,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M78" s="35" t="n">
+        <v>33</v>
+      </c>
+      <c r="N78" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="35" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R78" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S78" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -5013,6 +7214,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M79" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="N79" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q79" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R79" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S79" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5069,6 +7297,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M80" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="N80" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P80" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R80" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S80" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5125,6 +7380,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M81" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="N81" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P81" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R81" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S81" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5181,6 +7463,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M82" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="N82" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P82" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q82" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R82" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S82" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5237,6 +7546,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M83" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="N83" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P83" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q83" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R83" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S83" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5293,6 +7629,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M84" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="N84" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q84" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R84" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S84" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5349,6 +7712,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M85" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="N85" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="P85" s="35" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q85" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R85" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S85" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5405,6 +7795,33 @@
           <t>FS</t>
         </is>
       </c>
+      <c r="M86" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="N86" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q86" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R86" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S86" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -5461,6 +7878,33 @@
           <t>UX</t>
         </is>
       </c>
+      <c r="M87" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="N87" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="P87" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q87" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R87" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S87" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
@@ -5517,6 +7961,33 @@
           <t>UX</t>
         </is>
       </c>
+      <c r="M88" s="35" t="n">
+        <v>42</v>
+      </c>
+      <c r="N88" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="P88" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q88" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R88" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S88" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
@@ -5573,6 +8044,33 @@
           <t>UX</t>
         </is>
       </c>
+      <c r="M89" s="35" t="n">
+        <v>38</v>
+      </c>
+      <c r="N89" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="P89" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q89" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R89" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S89" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -5629,6 +8127,33 @@
           <t>FE</t>
         </is>
       </c>
+      <c r="M90" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="N90" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q90" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R90" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S90" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
@@ -5685,6 +8210,33 @@
           <t>FE</t>
         </is>
       </c>
+      <c r="M91" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="N91" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P91" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q91" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R91" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S91" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5741,6 +8293,33 @@
           <t>Sec</t>
         </is>
       </c>
+      <c r="M92" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="N92" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O92" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P92" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q92" s="35" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="R92" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S92" s="35" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5797,6 +8376,33 @@
           <t>Sec</t>
         </is>
       </c>
+      <c r="M93" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="N93" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P93" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q93" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R93" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S93" s="35" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -5853,6 +8459,33 @@
           <t>Sec</t>
         </is>
       </c>
+      <c r="M94" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="N94" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O94" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="P94" s="35" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q94" s="35" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="R94" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S94" s="35" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5909,6 +8542,33 @@
           <t>Sec</t>
         </is>
       </c>
+      <c r="M95" s="35" t="n">
+        <v>33</v>
+      </c>
+      <c r="N95" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O95" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P95" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q95" s="35" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="R95" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S95" s="35" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5965,6 +8625,33 @@
           <t>Sec</t>
         </is>
       </c>
+      <c r="M96" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="N96" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P96" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q96" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R96" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S96" s="35" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -6021,6 +8708,33 @@
           <t>Sec</t>
         </is>
       </c>
+      <c r="M97" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="N97" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q97" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R97" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S97" s="35" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6077,6 +8791,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M98" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="N98" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="P98" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q98" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R98" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S98" s="35" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6133,6 +8874,33 @@
           <t>Sec</t>
         </is>
       </c>
+      <c r="M99" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="N99" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q99" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R99" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S99" s="35" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6189,6 +8957,33 @@
           <t>Sec</t>
         </is>
       </c>
+      <c r="M100" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="N100" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q100" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R100" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S100" s="35" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6245,6 +9040,33 @@
           <t>Sec</t>
         </is>
       </c>
+      <c r="M101" s="35" t="n">
+        <v>36</v>
+      </c>
+      <c r="N101" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P101" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q101" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R101" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S101" s="35" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
@@ -6301,6 +9123,33 @@
           <t>DevOps</t>
         </is>
       </c>
+      <c r="M102" s="35" t="n">
+        <v>40</v>
+      </c>
+      <c r="N102" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="35" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q102" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R102" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S102" s="35" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
@@ -6357,6 +9206,33 @@
           <t>DevOps</t>
         </is>
       </c>
+      <c r="M103" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="N103" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q103" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R103" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S103" s="35" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
@@ -6413,6 +9289,33 @@
           <t>DevOps</t>
         </is>
       </c>
+      <c r="M104" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="N104" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q104" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R104" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S104" s="35" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -6469,6 +9372,33 @@
           <t>DevOps</t>
         </is>
       </c>
+      <c r="M105" s="35" t="n">
+        <v>33</v>
+      </c>
+      <c r="N105" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="35" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q105" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R105" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S105" s="35" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
@@ -6525,6 +9455,33 @@
           <t>DevOps</t>
         </is>
       </c>
+      <c r="M106" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="N106" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q106" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R106" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S106" s="35" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -6581,6 +9538,33 @@
           <t>DevOps</t>
         </is>
       </c>
+      <c r="M107" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="N107" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q107" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R107" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S107" s="35" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
@@ -6637,6 +9621,33 @@
           <t>DevOps</t>
         </is>
       </c>
+      <c r="M108" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="N108" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q108" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R108" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S108" s="35" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
@@ -6693,6 +9704,33 @@
           <t>DevOps</t>
         </is>
       </c>
+      <c r="M109" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="N109" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q109" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R109" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S109" s="35" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6749,6 +9787,33 @@
           <t>QA</t>
         </is>
       </c>
+      <c r="M110" s="35" t="n">
+        <v>44</v>
+      </c>
+      <c r="N110" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="P110" s="35" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q110" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R110" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S110" s="35" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6805,6 +9870,33 @@
           <t>QA</t>
         </is>
       </c>
+      <c r="M111" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="N111" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P111" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q111" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R111" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S111" s="35" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6861,6 +9953,33 @@
           <t>QA</t>
         </is>
       </c>
+      <c r="M112" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="N112" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O112" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P112" s="35" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q112" s="35" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="R112" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S112" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6917,6 +10036,33 @@
           <t>QA</t>
         </is>
       </c>
+      <c r="M113" s="35" t="n">
+        <v>50</v>
+      </c>
+      <c r="N113" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="P113" s="35" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q113" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R113" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S113" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6973,6 +10119,33 @@
           <t>QA</t>
         </is>
       </c>
+      <c r="M114" s="35" t="n">
+        <v>37</v>
+      </c>
+      <c r="N114" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O114" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="P114" s="35" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q114" s="35" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="R114" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S114" s="35" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -7029,6 +10202,33 @@
           <t>QA</t>
         </is>
       </c>
+      <c r="M115" s="35" t="n">
+        <v>39</v>
+      </c>
+      <c r="N115" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O115" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P115" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q115" s="35" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="R115" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S115" s="35" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -7085,6 +10285,33 @@
           <t>QA</t>
         </is>
       </c>
+      <c r="M116" s="35" t="n">
+        <v>46</v>
+      </c>
+      <c r="N116" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" s="35" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q116" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R116" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S116" s="35" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -7141,6 +10368,33 @@
           <t>QA</t>
         </is>
       </c>
+      <c r="M117" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="N117" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q117" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R117" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S117" s="35" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -7197,6 +10451,33 @@
           <t>QA</t>
         </is>
       </c>
+      <c r="M118" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="N118" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P118" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q118" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R118" s="36" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="S118" s="35" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -7253,6 +10534,33 @@
           <t>QA</t>
         </is>
       </c>
+      <c r="M119" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="N119" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q119" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R119" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S119" s="35" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -7309,6 +10617,33 @@
           <t>DevOps</t>
         </is>
       </c>
+      <c r="M120" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="N120" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q120" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R120" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S120" s="35" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
@@ -7365,6 +10700,33 @@
           <t>DevOps</t>
         </is>
       </c>
+      <c r="M121" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="N121" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q121" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R121" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S121" s="35" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
@@ -7421,6 +10783,33 @@
           <t>BE</t>
         </is>
       </c>
+      <c r="M122" s="35" t="n">
+        <v>42</v>
+      </c>
+      <c r="N122" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" s="35" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q122" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R122" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S122" s="35" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
@@ -7477,6 +10866,33 @@
           <t>QA</t>
         </is>
       </c>
+      <c r="M123" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="N123" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q123" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R123" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S123" s="35" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
@@ -7533,6 +10949,33 @@
           <t>All</t>
         </is>
       </c>
+      <c r="M124" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="N124" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q124" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R124" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S124" s="35" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
@@ -7589,27 +11032,1573 @@
           <t>DevOps</t>
         </is>
       </c>
+      <c r="M125" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="N125" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q125" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R125" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S125" s="35" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="10" t="n"/>
-      <c r="B126" s="10" t="n"/>
-      <c r="C126" s="10" t="n"/>
-      <c r="D126" s="10" t="n"/>
-      <c r="E126" s="10" t="n"/>
-      <c r="F126" s="10" t="n"/>
-      <c r="G126" s="10" t="n"/>
-      <c r="H126" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="I126" s="12">
-        <f>SUM(I2:I125)</f>
-        <v/>
-      </c>
-      <c r="J126" s="10" t="n"/>
-      <c r="K126" s="10" t="n"/>
-      <c r="L126" s="10" t="n"/>
+      <c r="A126" s="38" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="B126" s="38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C126" s="38" t="inlineStr">
+        <is>
+          <t>17. Real-Stack Gap Closure</t>
+        </is>
+      </c>
+      <c r="D126" s="39" t="inlineStr">
+        <is>
+          <t>Docker-capable build &amp; CI environment</t>
+        </is>
+      </c>
+      <c r="E126" s="39" t="inlineStr">
+        <is>
+          <t>Stand up a build host/runner with Docker so docker-compose + Testcontainers can run; wire into GitHub Actions. Single biggest unlock: every H2/stub PARTIAL depends on it.</t>
+        </is>
+      </c>
+      <c r="F126" s="38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G126" s="38" t="inlineStr">
+        <is>
+          <t>platform-infra</t>
+        </is>
+      </c>
+      <c r="H126" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I126" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="J126" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="39" t="inlineStr">
+        <is>
+          <t>CI job runs docker-compose stack + Testcontainers ITs green</t>
+        </is>
+      </c>
+      <c r="L126" s="38" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="M126" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N126" s="35" t="inlineStr"/>
+      <c r="O126" s="35" t="inlineStr"/>
+      <c r="P126" s="35" t="inlineStr"/>
+      <c r="Q126" s="35" t="inlineStr"/>
+      <c r="R126" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S126" s="35" t="inlineStr">
+        <is>
+          <t>R0</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="38" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="B127" s="38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C127" s="38" t="inlineStr">
+        <is>
+          <t>17. Real-Stack Gap Closure</t>
+        </is>
+      </c>
+      <c r="D127" s="39" t="inlineStr">
+        <is>
+          <t>H2 → real PostgreSQL per service</t>
+        </is>
+      </c>
+      <c r="E127" s="39" t="inlineStr">
+        <is>
+          <t>Replace H2-in-PG-mode test DBs with real PostgreSQL via docker-compose + Testcontainers ITs for all 12 persistence-bearing services; verify Flyway migrations against PG 16.</t>
+        </is>
+      </c>
+      <c r="F127" s="38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G127" s="38" t="inlineStr">
+        <is>
+          <t>all data services</t>
+        </is>
+      </c>
+      <c r="H127" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I127" s="38" t="n">
+        <v>18</v>
+      </c>
+      <c r="J127" s="38" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="K127" s="39" t="inlineStr">
+        <is>
+          <t>Repository ITs green on real PostgreSQL for 12 services</t>
+        </is>
+      </c>
+      <c r="L127" s="38" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="M127" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="N127" s="35" t="inlineStr"/>
+      <c r="O127" s="35" t="inlineStr"/>
+      <c r="P127" s="35" t="inlineStr"/>
+      <c r="Q127" s="35" t="inlineStr"/>
+      <c r="R127" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S127" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="38" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="B128" s="38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C128" s="38" t="inlineStr">
+        <is>
+          <t>17. Real-Stack Gap Closure</t>
+        </is>
+      </c>
+      <c r="D128" s="39" t="inlineStr">
+        <is>
+          <t>Redis wiring (cache/TTL/idempotency)</t>
+        </is>
+      </c>
+      <c r="E128" s="39" t="inlineStr">
+        <is>
+          <t>Replace in-memory stores with Redis: rate-quote TTL store (rate-fx), idempotency keys (transaction-mgmt/api-gateway), config cache (config-registry).</t>
+        </is>
+      </c>
+      <c r="F128" s="38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G128" s="38" t="inlineStr">
+        <is>
+          <t>rate-fx, txn-mgmt, config-registry</t>
+        </is>
+      </c>
+      <c r="H128" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I128" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="J128" s="38" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="K128" s="39" t="inlineStr">
+        <is>
+          <t>Redis-backed stores with ITs</t>
+        </is>
+      </c>
+      <c r="L128" s="38" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="M128" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N128" s="35" t="inlineStr"/>
+      <c r="O128" s="35" t="inlineStr"/>
+      <c r="P128" s="35" t="inlineStr"/>
+      <c r="Q128" s="35" t="inlineStr"/>
+      <c r="R128" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S128" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="38" t="inlineStr">
+        <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="B129" s="38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C129" s="38" t="inlineStr">
+        <is>
+          <t>17. Real-Stack Gap Closure</t>
+        </is>
+      </c>
+      <c r="D129" s="39" t="inlineStr">
+        <is>
+          <t>Kafka producer + Schema Registry</t>
+        </is>
+      </c>
+      <c r="E129" s="39" t="inlineStr">
+        <is>
+          <t>Implement KafkaEventPublisher behind lib-events EventPublisher; outbox publishers drain to Kafka; notification-webhook consumes payment.approved; Schema Registry with subject naming + compatibility rules.</t>
+        </is>
+      </c>
+      <c r="F129" s="38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G129" s="38" t="inlineStr">
+        <is>
+          <t>lib-events, all outbox services</t>
+        </is>
+      </c>
+      <c r="H129" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I129" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="J129" s="38" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="K129" s="39" t="inlineStr">
+        <is>
+          <t>Events flow producer→Kafka→consumer in compose stack</t>
+        </is>
+      </c>
+      <c r="L129" s="38" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="M129" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="N129" s="35" t="inlineStr"/>
+      <c r="O129" s="35" t="inlineStr"/>
+      <c r="P129" s="35" t="inlineStr"/>
+      <c r="Q129" s="35" t="inlineStr"/>
+      <c r="R129" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S129" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="38" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="B130" s="38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C130" s="38" t="inlineStr">
+        <is>
+          <t>17. Real-Stack Gap Closure</t>
+        </is>
+      </c>
+      <c r="D130" s="39" t="inlineStr">
+        <is>
+          <t>Stub→REST client flip, E2E verified</t>
+        </is>
+      </c>
+      <c r="E130" s="39" t="inlineStr">
+        <is>
+          <t>Promote Rest*Client @Primary impls to verified: payment-executor's 7 clients and ops-partner-bff's 10 clients exercised against live services on the compose stack; delete/demote stubs to test scope.</t>
+        </is>
+      </c>
+      <c r="F130" s="38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G130" s="38" t="inlineStr">
+        <is>
+          <t>payment-executor, ops-partner-bff</t>
+        </is>
+      </c>
+      <c r="H130" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I130" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="J130" s="38" t="inlineStr">
+        <is>
+          <t>17.1,17.2</t>
+        </is>
+      </c>
+      <c r="K130" s="39" t="inlineStr">
+        <is>
+          <t>Inter-service REST calls verified E2E; stubs test-only</t>
+        </is>
+      </c>
+      <c r="L130" s="38" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="M130" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N130" s="35" t="inlineStr"/>
+      <c r="O130" s="35" t="inlineStr"/>
+      <c r="P130" s="35" t="inlineStr"/>
+      <c r="Q130" s="35" t="inlineStr"/>
+      <c r="R130" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S130" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="38" t="inlineStr">
+        <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="B131" s="38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C131" s="38" t="inlineStr">
+        <is>
+          <t>17. Real-Stack Gap Closure</t>
+        </is>
+      </c>
+      <c r="D131" s="39" t="inlineStr">
+        <is>
+          <t>Registry persistence (scheme/rule/treasury)</t>
+        </is>
+      </c>
+      <c r="E131" s="39" t="inlineStr">
+        <is>
+          <t>Persist Scheme, Routing-Rule and Treasury registries in config-registry (currently in-memory/seed): entities, Flyway, CRUD endpoints, effective-dating.</t>
+        </is>
+      </c>
+      <c r="F131" s="38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G131" s="38" t="inlineStr">
+        <is>
+          <t>config-registry</t>
+        </is>
+      </c>
+      <c r="H131" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I131" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="J131" s="38" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="K131" s="39" t="inlineStr">
+        <is>
+          <t>Registries survive restart; CRUD + ITs green</t>
+        </is>
+      </c>
+      <c r="L131" s="38" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="M131" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N131" s="35" t="inlineStr"/>
+      <c r="O131" s="35" t="inlineStr"/>
+      <c r="P131" s="35" t="inlineStr"/>
+      <c r="Q131" s="35" t="inlineStr"/>
+      <c r="R131" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S131" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="38" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="B132" s="38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C132" s="38" t="inlineStr">
+        <is>
+          <t>17. Real-Stack Gap Closure</t>
+        </is>
+      </c>
+      <c r="D132" s="39" t="inlineStr">
+        <is>
+          <t>MongoDB merchant/QR mirror</t>
+        </is>
+      </c>
+      <c r="E132" s="39" t="inlineStr">
+        <is>
+          <t>Stand up MongoDB for merchant-qr-data (per architecture diagram); move lookup store from memory to Mongo; nightly sync job skeleton.</t>
+        </is>
+      </c>
+      <c r="F132" s="38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G132" s="38" t="inlineStr">
+        <is>
+          <t>merchant-qr-data</t>
+        </is>
+      </c>
+      <c r="H132" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I132" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="J132" s="38" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="K132" s="39" t="inlineStr">
+        <is>
+          <t>Mongo-backed merchant lookup with ITs</t>
+        </is>
+      </c>
+      <c r="L132" s="38" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="M132" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N132" s="35" t="inlineStr"/>
+      <c r="O132" s="35" t="inlineStr"/>
+      <c r="P132" s="35" t="inlineStr"/>
+      <c r="Q132" s="35" t="inlineStr"/>
+      <c r="R132" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S132" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="38" t="inlineStr">
+        <is>
+          <t>17.8</t>
+        </is>
+      </c>
+      <c r="B133" s="38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C133" s="38" t="inlineStr">
+        <is>
+          <t>17. Real-Stack Gap Closure</t>
+        </is>
+      </c>
+      <c r="D133" s="39" t="inlineStr">
+        <is>
+          <t>Object storage (MinIO) for files</t>
+        </is>
+      </c>
+      <c r="E133" s="39" t="inlineStr">
+        <is>
+          <t>S3-compatible MinIO in compose; statements, recon files and ZP batch files stored/retrieved via a small lib-storage client.</t>
+        </is>
+      </c>
+      <c r="F133" s="38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G133" s="38" t="inlineStr">
+        <is>
+          <t>settlement, scheme-adapter, BFF</t>
+        </is>
+      </c>
+      <c r="H133" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I133" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="J133" s="38" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="K133" s="39" t="inlineStr">
+        <is>
+          <t>Files round-trip through MinIO</t>
+        </is>
+      </c>
+      <c r="L133" s="38" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="M133" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N133" s="35" t="inlineStr"/>
+      <c r="O133" s="35" t="inlineStr"/>
+      <c r="P133" s="35" t="inlineStr"/>
+      <c r="Q133" s="35" t="inlineStr"/>
+      <c r="R133" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S133" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="38" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="B134" s="38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C134" s="38" t="inlineStr">
+        <is>
+          <t>18. Missing Components</t>
+        </is>
+      </c>
+      <c r="D134" s="39" t="inlineStr">
+        <is>
+          <t>ops-partner-bff legitimization &amp; real wiring</t>
+        </is>
+      </c>
+      <c r="E134" s="39" t="inlineStr">
+        <is>
+          <t>The BFF was built ahead of tickets (19 endpoints + 18 test classes). Legitimize in WBS; wire its 10 clients to real services; add auth pass-through.</t>
+        </is>
+      </c>
+      <c r="F134" s="38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G134" s="38" t="inlineStr">
+        <is>
+          <t>ops-partner-bff</t>
+        </is>
+      </c>
+      <c r="H134" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I134" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="J134" s="38" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="K134" s="39" t="inlineStr">
+        <is>
+          <t>BFF serves both UIs from live services</t>
+        </is>
+      </c>
+      <c r="L134" s="38" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="M134" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N134" s="35" t="inlineStr"/>
+      <c r="O134" s="35" t="inlineStr"/>
+      <c r="P134" s="35" t="inlineStr"/>
+      <c r="Q134" s="35" t="inlineStr"/>
+      <c r="R134" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S134" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="38" t="inlineStr">
+        <is>
+          <t>18.2</t>
+        </is>
+      </c>
+      <c r="B135" s="38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C135" s="38" t="inlineStr">
+        <is>
+          <t>18. Missing Components</t>
+        </is>
+      </c>
+      <c r="D135" s="39" t="inlineStr">
+        <is>
+          <t>Nginx WAF edge</t>
+        </is>
+      </c>
+      <c r="E135" s="39" t="inlineStr">
+        <is>
+          <t>Nginx reverse proxy + WAF rules in front of api-gateway and the UIs per the architecture diagram (decision 18.7 governs final edge shape).</t>
+        </is>
+      </c>
+      <c r="F135" s="38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G135" s="38" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="H135" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I135" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="J135" s="38" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="K135" s="39" t="inlineStr">
+        <is>
+          <t>Nginx fronts the compose stack with WAF ruleset</t>
+        </is>
+      </c>
+      <c r="L135" s="38" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="M135" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N135" s="35" t="inlineStr"/>
+      <c r="O135" s="35" t="inlineStr"/>
+      <c r="P135" s="35" t="inlineStr"/>
+      <c r="Q135" s="35" t="inlineStr"/>
+      <c r="R135" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S135" s="35" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="38" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="B136" s="38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C136" s="38" t="inlineStr">
+        <is>
+          <t>18. Missing Components</t>
+        </is>
+      </c>
+      <c r="D136" s="39" t="inlineStr">
+        <is>
+          <t>SFTP Gateway service</t>
+        </is>
+      </c>
+      <c r="E136" s="39" t="inlineStr">
+        <is>
+          <t>Dedicated SFTP gateway (per architecture diagram) brokering KFTC batch file exchange: inbound/outbound directories, PGP encrypt/decrypt, key mgmt, pickup/drop schedule.</t>
+        </is>
+      </c>
+      <c r="F136" s="38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G136" s="38" t="inlineStr">
+        <is>
+          <t>sftp-gateway</t>
+        </is>
+      </c>
+      <c r="H136" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I136" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="J136" s="38" t="inlineStr">
+        <is>
+          <t>17.8</t>
+        </is>
+      </c>
+      <c r="K136" s="39" t="inlineStr">
+        <is>
+          <t>ZP files flow disk↔SFTP↔adapter in compose stack</t>
+        </is>
+      </c>
+      <c r="L136" s="38" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="M136" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N136" s="35" t="inlineStr"/>
+      <c r="O136" s="35" t="inlineStr"/>
+      <c r="P136" s="35" t="inlineStr"/>
+      <c r="Q136" s="35" t="inlineStr"/>
+      <c r="R136" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S136" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="38" t="inlineStr">
+        <is>
+          <t>18.4</t>
+        </is>
+      </c>
+      <c r="B137" s="38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C137" s="38" t="inlineStr">
+        <is>
+          <t>18. Missing Components</t>
+        </is>
+      </c>
+      <c r="D137" s="39" t="inlineStr">
+        <is>
+          <t>Real authentication (replace demo login)</t>
+        </is>
+      </c>
+      <c r="E137" s="39" t="inlineStr">
+        <is>
+          <t>Replace password=demo stub: auth-identity issues JWTs (OAuth2 password/client-credentials), BFF validates, RBAC roles enforced, refresh rotation, login rate-limit.</t>
+        </is>
+      </c>
+      <c r="F137" s="38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G137" s="38" t="inlineStr">
+        <is>
+          <t>auth-identity, ops-partner-bff, UIs</t>
+        </is>
+      </c>
+      <c r="H137" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I137" s="38" t="n">
+        <v>10</v>
+      </c>
+      <c r="J137" s="38" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="K137" s="39" t="inlineStr">
+        <is>
+          <t>Login works end-to-end with real JWT + RBAC</t>
+        </is>
+      </c>
+      <c r="L137" s="38" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="M137" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="N137" s="35" t="inlineStr"/>
+      <c r="O137" s="35" t="inlineStr"/>
+      <c r="P137" s="35" t="inlineStr"/>
+      <c r="Q137" s="35" t="inlineStr"/>
+      <c r="R137" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S137" s="35" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="38" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="B138" s="38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C138" s="38" t="inlineStr">
+        <is>
+          <t>18. Missing Components</t>
+        </is>
+      </c>
+      <c r="D138" s="39" t="inlineStr">
+        <is>
+          <t>UI contract-drift prevention</t>
+        </is>
+      </c>
+      <c r="E138" s="39" t="inlineStr">
+        <is>
+          <t>Per-slice Vitest contract tests pinned to the BFF wire contract (already started); add CI check that fails on BFF DTO/UI field drift; Playwright-free smoke via vitest+jsdom.</t>
+        </is>
+      </c>
+      <c r="F138" s="38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G138" s="38" t="inlineStr">
+        <is>
+          <t>admin-ui, partner-portal-ui</t>
+        </is>
+      </c>
+      <c r="H138" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I138" s="38" t="n">
+        <v>4</v>
+      </c>
+      <c r="J138" s="38" t="inlineStr">
+        <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="K138" s="39" t="inlineStr">
+        <is>
+          <t>CI fails on contract drift; 19 pages smoke-tested</t>
+        </is>
+      </c>
+      <c r="L138" s="38" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="M138" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N138" s="35" t="inlineStr"/>
+      <c r="O138" s="35" t="inlineStr"/>
+      <c r="P138" s="35" t="inlineStr"/>
+      <c r="Q138" s="35" t="inlineStr"/>
+      <c r="R138" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S138" s="35" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="38" t="inlineStr">
+        <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="B139" s="38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C139" s="38" t="inlineStr">
+        <is>
+          <t>18. Missing Components</t>
+        </is>
+      </c>
+      <c r="D139" s="39" t="inlineStr">
+        <is>
+          <t>docker-compose E2E money-path harness</t>
+        </is>
+      </c>
+      <c r="E139" s="39" t="inlineStr">
+        <is>
+          <t>One command brings up the full stack + seeded demo data; scripted E2E: quote→route→prefund deduct→execute→ZP simulate→commit→settlement booking+rounding residual→webhook; asserts ledger invariants.</t>
+        </is>
+      </c>
+      <c r="F139" s="38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G139" s="38" t="inlineStr">
+        <is>
+          <t>qa-platform</t>
+        </is>
+      </c>
+      <c r="H139" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I139" s="38" t="n">
+        <v>8</v>
+      </c>
+      <c r="J139" s="38" t="inlineStr">
+        <is>
+          <t>17.1,17.5</t>
+        </is>
+      </c>
+      <c r="K139" s="39" t="inlineStr">
+        <is>
+          <t>Money-path E2E green in CI</t>
+        </is>
+      </c>
+      <c r="L139" s="38" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="M139" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N139" s="35" t="inlineStr"/>
+      <c r="O139" s="35" t="inlineStr"/>
+      <c r="P139" s="35" t="inlineStr"/>
+      <c r="Q139" s="35" t="inlineStr"/>
+      <c r="R139" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S139" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="38" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="B140" s="38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C140" s="38" t="inlineStr">
+        <is>
+          <t>18. Missing Components</t>
+        </is>
+      </c>
+      <c r="D140" s="39" t="inlineStr">
+        <is>
+          <t>Stack decision record (ADR)</t>
+        </is>
+      </c>
+      <c r="E140" s="39" t="inlineStr">
+        <is>
+          <t>Resolve user-pending contradictions: Kafka vs RabbitMQ, Spring Cloud Gateway vs Nginx, MongoDB keep/drop, Rocky Linux images, Elasticsearch role. Write ADRs; align code.</t>
+        </is>
+      </c>
+      <c r="F140" s="38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G140" s="38" t="inlineStr">
+        <is>
+          <t>architecture</t>
+        </is>
+      </c>
+      <c r="H140" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I140" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J140" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="39" t="inlineStr">
+        <is>
+          <t>ADR-001..005 merged; stack matches one source of truth</t>
+        </is>
+      </c>
+      <c r="L140" s="38" t="inlineStr">
+        <is>
+          <t>Architect</t>
+        </is>
+      </c>
+      <c r="M140" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N140" s="35" t="inlineStr"/>
+      <c r="O140" s="35" t="inlineStr"/>
+      <c r="P140" s="35" t="inlineStr"/>
+      <c r="Q140" s="35" t="inlineStr"/>
+      <c r="R140" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S140" s="35" t="inlineStr">
+        <is>
+          <t>R0</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="38" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="B141" s="38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C141" s="38" t="inlineStr">
+        <is>
+          <t>20. Phase-2+ Scheme Adapters</t>
+        </is>
+      </c>
+      <c r="D141" s="39" t="inlineStr">
+        <is>
+          <t>KHQR adapter (Cambodia)</t>
+        </is>
+      </c>
+      <c r="E141" s="39" t="inlineStr">
+        <is>
+          <t>Bakong KHQR scheme adapter: EMVCo profile, member bank API, settlement files. Expand WBS when partner contract lands.</t>
+        </is>
+      </c>
+      <c r="F141" s="38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G141" s="38" t="inlineStr">
+        <is>
+          <t>scheme-adapter-khqr</t>
+        </is>
+      </c>
+      <c r="H141" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I141" s="38" t="n">
+        <v>40</v>
+      </c>
+      <c r="J141" s="38" t="inlineStr">
+        <is>
+          <t>9.1,16.2</t>
+        </is>
+      </c>
+      <c r="K141" s="39" t="inlineStr">
+        <is>
+          <t>KHQR adapter certified</t>
+        </is>
+      </c>
+      <c r="L141" s="38" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="M141" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N141" s="35" t="inlineStr"/>
+      <c r="O141" s="35" t="inlineStr"/>
+      <c r="P141" s="35" t="inlineStr"/>
+      <c r="Q141" s="35" t="inlineStr"/>
+      <c r="R141" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S141" s="35" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="38" t="inlineStr">
+        <is>
+          <t>20.2</t>
+        </is>
+      </c>
+      <c r="B142" s="38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C142" s="38" t="inlineStr">
+        <is>
+          <t>20. Phase-2+ Scheme Adapters</t>
+        </is>
+      </c>
+      <c r="D142" s="39" t="inlineStr">
+        <is>
+          <t>QPay adapter (Mongolia)</t>
+        </is>
+      </c>
+      <c r="E142" s="39" t="inlineStr">
+        <is>
+          <t>QPay scheme adapter. Expand WBS when partner contract lands.</t>
+        </is>
+      </c>
+      <c r="F142" s="38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G142" s="38" t="inlineStr">
+        <is>
+          <t>scheme-adapter-qpay</t>
+        </is>
+      </c>
+      <c r="H142" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I142" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="J142" s="38" t="inlineStr">
+        <is>
+          <t>9.1,16.2</t>
+        </is>
+      </c>
+      <c r="K142" s="39" t="inlineStr">
+        <is>
+          <t>QPay adapter certified</t>
+        </is>
+      </c>
+      <c r="L142" s="38" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="M142" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N142" s="35" t="inlineStr"/>
+      <c r="O142" s="35" t="inlineStr"/>
+      <c r="P142" s="35" t="inlineStr"/>
+      <c r="Q142" s="35" t="inlineStr"/>
+      <c r="R142" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S142" s="35" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="38" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="B143" s="38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C143" s="38" t="inlineStr">
+        <is>
+          <t>20. Phase-2+ Scheme Adapters</t>
+        </is>
+      </c>
+      <c r="D143" s="39" t="inlineStr">
+        <is>
+          <t>QRIS adapter (Indonesia)</t>
+        </is>
+      </c>
+      <c r="E143" s="39" t="inlineStr">
+        <is>
+          <t>QRIS scheme adapter. Expand WBS when partner contract lands.</t>
+        </is>
+      </c>
+      <c r="F143" s="38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G143" s="38" t="inlineStr">
+        <is>
+          <t>scheme-adapter-qris</t>
+        </is>
+      </c>
+      <c r="H143" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I143" s="38" t="n">
+        <v>40</v>
+      </c>
+      <c r="J143" s="38" t="inlineStr">
+        <is>
+          <t>9.1,16.2</t>
+        </is>
+      </c>
+      <c r="K143" s="39" t="inlineStr">
+        <is>
+          <t>QRIS adapter certified</t>
+        </is>
+      </c>
+      <c r="L143" s="38" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="M143" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N143" s="35" t="inlineStr"/>
+      <c r="O143" s="35" t="inlineStr"/>
+      <c r="P143" s="35" t="inlineStr"/>
+      <c r="Q143" s="35" t="inlineStr"/>
+      <c r="R143" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S143" s="35" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="38" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="B144" s="38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C144" s="38" t="inlineStr">
+        <is>
+          <t>20. Phase-2+ Scheme Adapters</t>
+        </is>
+      </c>
+      <c r="D144" s="39" t="inlineStr">
+        <is>
+          <t>SBP adapter (Russia)</t>
+        </is>
+      </c>
+      <c r="E144" s="39" t="inlineStr">
+        <is>
+          <t>SBP scheme adapter (sanctions/compliance review first). Expand WBS when cleared.</t>
+        </is>
+      </c>
+      <c r="F144" s="38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G144" s="38" t="inlineStr">
+        <is>
+          <t>scheme-adapter-sbp</t>
+        </is>
+      </c>
+      <c r="H144" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I144" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="J144" s="38" t="inlineStr">
+        <is>
+          <t>9.1,16.2,13.8</t>
+        </is>
+      </c>
+      <c r="K144" s="39" t="inlineStr">
+        <is>
+          <t>SBP adapter certified</t>
+        </is>
+      </c>
+      <c r="L144" s="38" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="M144" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N144" s="35" t="inlineStr"/>
+      <c r="O144" s="35" t="inlineStr"/>
+      <c r="P144" s="35" t="inlineStr"/>
+      <c r="Q144" s="35" t="inlineStr"/>
+      <c r="R144" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S144" s="35" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="38" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="B145" s="38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C145" s="38" t="inlineStr">
+        <is>
+          <t>20. Phase-2+ Scheme Adapters</t>
+        </is>
+      </c>
+      <c r="D145" s="39" t="inlineStr">
+        <is>
+          <t>PromptPay adapter (Thailand)</t>
+        </is>
+      </c>
+      <c r="E145" s="39" t="inlineStr">
+        <is>
+          <t>PromptPay scheme adapter. Expand WBS when partner contract lands.</t>
+        </is>
+      </c>
+      <c r="F145" s="38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G145" s="38" t="inlineStr">
+        <is>
+          <t>scheme-adapter-promptpay</t>
+        </is>
+      </c>
+      <c r="H145" s="38" t="inlineStr">
+        <is>
+          <t>Audit 2026-06-10 / WBS v3 re-baseline</t>
+        </is>
+      </c>
+      <c r="I145" s="38" t="n">
+        <v>35</v>
+      </c>
+      <c r="J145" s="38" t="inlineStr">
+        <is>
+          <t>9.1,16.2</t>
+        </is>
+      </c>
+      <c r="K145" s="39" t="inlineStr">
+        <is>
+          <t>PromptPay adapter certified</t>
+        </is>
+      </c>
+      <c r="L145" s="38" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="M145" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N145" s="35" t="inlineStr"/>
+      <c r="O145" s="35" t="inlineStr"/>
+      <c r="P145" s="35" t="inlineStr"/>
+      <c r="Q145" s="35" t="inlineStr"/>
+      <c r="R145" s="37" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S145" s="35" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L125"/>
@@ -7618,6 +12607,574 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>GMEPay+ — Completion Plan v3 (re-baselined after the 2026-06-10 code audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="41" t="inlineStr">
+        <is>
+          <t>Every WBS code is mapped to one executable completion phase R0–R8. Sequence is dependency-true: R0 unlocks Testcontainers/compose; R1 makes persistence real; R2 proves the money path E2E; R3–R6 are productionization; R7 is external-party bound; R8 is launch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>WBS codes</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Tickets</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>% D+P</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>Exit gate</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>External blockers</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>R0</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>Decisions &amp; build environment</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>AI agents + GME + user</t>
+        </is>
+      </c>
+      <c r="D5" s="43" t="inlineStr">
+        <is>
+          <t>1.1 1.2 1.3 1.4 2.1 2.2 2.3 17.1 18.7</t>
+        </is>
+      </c>
+      <c r="E5" s="44" t="n">
+        <v>190</v>
+      </c>
+      <c r="F5" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" s="44" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" s="44" t="n">
+        <v>144</v>
+      </c>
+      <c r="I5" s="44" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="J5" s="43" t="inlineStr">
+        <is>
+          <t>Docker-capable CI green; stack ADRs signed (Kafka/RabbitMQ, Gateway/Nginx, Mongo)</t>
+        </is>
+      </c>
+      <c r="K5" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>Persistence &amp; real wiring (gap closure)</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>2.4 2.5 3.1 3.2 3.3 3.4 3.5 3.6 3.7 4.1 4.6 4.7 6.1 6.2 6.3 6.4 17.2 17.3 17.4 17.6 17.7 17.8</t>
+        </is>
+      </c>
+      <c r="E6" s="44" t="n">
+        <v>424</v>
+      </c>
+      <c r="F6" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="44" t="n">
+        <v>81</v>
+      </c>
+      <c r="H6" s="44" t="n">
+        <v>340</v>
+      </c>
+      <c r="I6" s="44" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="J6" s="43" t="inlineStr">
+        <is>
+          <t>All 12 services on real PostgreSQL; Redis/Kafka/Mongo/MinIO wired; registries persistent</t>
+        </is>
+      </c>
+      <c r="K6" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>Money-path E2E on compose stack</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>4.2 4.3 4.4 4.5 4.8 4.9 5.1 5.2 5.3 5.4 5.5 5.6 5.7 5.8 6.5 7.1 7.2 7.3 7.4 7.6 8.3 8.4 8.5 8.6 8.7 9.1 9.4 9.9 15.3 15.4 17.5 18.1 18.3 18.6</t>
+        </is>
+      </c>
+      <c r="E7" s="44" t="n">
+        <v>715</v>
+      </c>
+      <c r="F7" s="44" t="n">
+        <v>20</v>
+      </c>
+      <c r="G7" s="44" t="n">
+        <v>131</v>
+      </c>
+      <c r="H7" s="44" t="n">
+        <v>564</v>
+      </c>
+      <c r="I7" s="44" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="J7" s="43" t="inlineStr">
+        <is>
+          <t>Scripted E2E quote→commit→settlement+rounding residual→webhook green in CI</t>
+        </is>
+      </c>
+      <c r="K7" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>Edge &amp; security</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>AI agents + GME Security</t>
+        </is>
+      </c>
+      <c r="D8" s="43" t="inlineStr">
+        <is>
+          <t>8.1 8.2 8.8 13.1 13.2 13.3 13.4 13.5 13.6 13.9 18.2 18.4</t>
+        </is>
+      </c>
+      <c r="E8" s="44" t="n">
+        <v>272</v>
+      </c>
+      <c r="F8" s="44" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" s="44" t="n">
+        <v>24</v>
+      </c>
+      <c r="H8" s="44" t="n">
+        <v>240</v>
+      </c>
+      <c r="I8" s="44" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="J8" s="43" t="inlineStr">
+        <is>
+          <t>Nginx WAF up; real JWT auth + RBAC; Vault for secrets; HMAC/idempotency at edge</t>
+        </is>
+      </c>
+      <c r="K8" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>UI completion against live BFF</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>2.6 10.1 10.2 10.3 10.4 10.5 10.6 10.7 10.8 10.9 10.10 10.11 11.1 11.2 11.3 11.4 11.5 11.6 11.7 12.1 12.2 12.3 12.4 12.5 18.5</t>
+        </is>
+      </c>
+      <c r="E9" s="44" t="n">
+        <v>717</v>
+      </c>
+      <c r="F9" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="44" t="n">
+        <v>80</v>
+      </c>
+      <c r="H9" s="44" t="n">
+        <v>637</v>
+      </c>
+      <c r="I9" s="44" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="J9" s="43" t="inlineStr">
+        <is>
+          <t>All admin + portal WBS screens functional vs live BFF; contract-drift CI gate</t>
+        </is>
+      </c>
+      <c r="K9" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>Infrastructure &amp; observability</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>GME DevOps (agents author IaC)</t>
+        </is>
+      </c>
+      <c r="D10" s="43" t="inlineStr">
+        <is>
+          <t>14.1 14.2 14.3 14.4 14.5 14.6 14.7 14.8 16.1</t>
+        </is>
+      </c>
+      <c r="E10" s="44" t="n">
+        <v>268</v>
+      </c>
+      <c r="F10" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="44" t="n">
+        <v>268</v>
+      </c>
+      <c r="I10" s="44" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J10" s="43" t="inlineStr">
+        <is>
+          <t>Staging on K8s via CI/CD; OTel+Prometheus/Grafana+ELK+Jaeger; backup/DR drill</t>
+        </is>
+      </c>
+      <c r="K10" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>Hardening, performance, pen test</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>Agents author; GME validates</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>13.10 15.1 15.2 15.5 15.7 15.8 15.10</t>
+        </is>
+      </c>
+      <c r="E11" s="44" t="n">
+        <v>256</v>
+      </c>
+      <c r="F11" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="44" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" s="44" t="n">
+        <v>241</v>
+      </c>
+      <c r="I11" s="44" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="J11" s="43" t="inlineStr">
+        <is>
+          <t>NFR-10 load targets met; pen test passed; regression suite green</t>
+        </is>
+      </c>
+      <c r="K11" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="45" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="B12" s="46" t="inlineStr">
+        <is>
+          <t>Compliance &amp; certification</t>
+        </is>
+      </c>
+      <c r="C12" s="46" t="inlineStr">
+        <is>
+          <t>GME + external parties</t>
+        </is>
+      </c>
+      <c r="D12" s="46" t="inlineStr">
+        <is>
+          <t>7.5 8.9 8.10 9.2 9.3 9.5 9.6 9.7 9.8 9.10 13.7 13.8 15.6</t>
+        </is>
+      </c>
+      <c r="E12" s="47" t="n">
+        <v>392</v>
+      </c>
+      <c r="F12" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="47" t="n">
+        <v>41</v>
+      </c>
+      <c r="H12" s="47" t="n">
+        <v>348</v>
+      </c>
+      <c r="I12" s="47" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="J12" s="46" t="inlineStr">
+        <is>
+          <t>KFTC/ZeroPay certified; BOK FX1014/1015 verified; Hometax integrated; AML live</t>
+        </is>
+      </c>
+      <c r="K12" s="46" t="inlineStr">
+        <is>
+          <t>KFTC test env, BOK OI-03, Hometax OI-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>UAT, go-live &amp; hypercare</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>GME business + partners</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="inlineStr">
+        <is>
+          <t>1.5 1.6 15.9 16.2 16.3 16.4 16.5 16.6 20.1 20.2 20.3 20.4 20.5</t>
+        </is>
+      </c>
+      <c r="E13" s="44" t="n">
+        <v>253</v>
+      </c>
+      <c r="F13" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="44" t="n">
+        <v>252</v>
+      </c>
+      <c r="I13" s="44" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J13" s="43" t="inlineStr">
+        <is>
+          <t>UAT signed; production cutover rehearsed; 14-day hypercare; Phase-2 adapters start</t>
+        </is>
+      </c>
+      <c r="K13" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="48" t="inlineStr"/>
+      <c r="B14" s="48" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C14" s="48" t="inlineStr"/>
+      <c r="D14" s="48" t="inlineStr"/>
+      <c r="E14" s="49" t="n">
+        <v>3487</v>
+      </c>
+      <c r="F14" s="49" t="n">
+        <v>41</v>
+      </c>
+      <c r="G14" s="49" t="n">
+        <v>412</v>
+      </c>
+      <c r="H14" s="49" t="n">
+        <v>3034</v>
+      </c>
+      <c r="I14" s="49" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="J14" s="49" t="inlineStr"/>
+      <c r="K14" s="49" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8262,7 +13819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8635,7 +14192,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Documentation/GMEPay+_WBS.xlsx
+++ b/Documentation/GMEPay+_WBS.xlsx
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S145"/>
+  <dimension ref="A1:S154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="R71" s="36" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>IN PROGRESS | SUPERSEDED — see WS 21 / docs/PARTNER_SETUP_PLAN.md</t>
         </is>
       </c>
       <c r="S71" s="35" t="inlineStr">
@@ -12597,6 +12597,753 @@
       <c r="S145" s="35" t="inlineStr">
         <is>
           <t>R8</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="B146" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C146" s="8" t="inlineStr">
+        <is>
+          <t>21. Partner Setup re-baseline</t>
+        </is>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t>WS 21 — Partner Setup re-baseline (8 vertical slices)</t>
+        </is>
+      </c>
+      <c r="E146" s="8" t="inlineStr">
+        <is>
+          <t>Re-baselines Partner Setup against DAT-03 §4.3 + PRD-07 §5.3: the 4-field demo (/partners/new with partnerId/type/settlementCurrency/settlementRoundingMode) is replaced by an 8-step wizard delivered as 8 vertical slices (21.1–21.8). Architecture locked by ADR-006..014. Sole source of truth: docs/PARTNER_SETUP_PLAN.md.</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G146" s="8" t="inlineStr">
+        <is>
+          <t>Cross-cutting (config-registry + ops-partner-bff + admin-ui + auth-identity + prefunding + notification-webhook + kyb-adapter)</t>
+        </is>
+      </c>
+      <c r="H146" s="8" t="inlineStr">
+        <is>
+          <t>PARTNER_SETUP_PLAN.md; DAT-03 §4.3; PRD-07 §5.3; ADR-006..014</t>
+        </is>
+      </c>
+      <c r="I146" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="J146" s="8" t="inlineStr">
+        <is>
+          <t>10.3 (superseded), 8.x, 13.x</t>
+        </is>
+      </c>
+      <c r="K146" s="8" t="inlineStr">
+        <is>
+          <t>8-step partner onboarding wizard, end-to-end FSM, full audit + 4-eyes + KYB + bitemporal aggregate</t>
+        </is>
+      </c>
+      <c r="L146" s="8" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M146" s="35" t="n">
+        <v>179</v>
+      </c>
+      <c r="N146" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" s="35" t="n">
+        <v>179</v>
+      </c>
+      <c r="Q146" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R146" s="36" t="inlineStr">
+        <is>
+          <t>NOT STARTED (re-baselined 2026-06-11)</t>
+        </is>
+      </c>
+      <c r="S146" s="35" t="inlineStr">
+        <is>
+          <t>R0..R3</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t>21. Partner Setup re-baseline</t>
+        </is>
+      </c>
+      <c r="D147" s="8" t="inlineStr">
+        <is>
+          <t>Slice 1 — Identity + Foundation</t>
+        </is>
+      </c>
+      <c r="E147" s="8" t="inlineStr">
+        <is>
+          <t>Wizard scaffold + step 1 (Identity). Foundation primitives every later slice depends on: resolve String↔Long Partner ID schism (adopt partner_id BIGINT surrogate + partner_code VARCHAR(20) unique business key per ADR-013 Expand/Backfill/Contract); collapse 5 Partner DTO shapes into canonical PartnerView (read) + PartnerCommand (write) in lib-api-contracts. Bitemporal partner table (ADR-010 SCD-Type-6, valid_from/to + recorded_at/superseded_at + current-flag). change_request table + Spring State Machine (ADR-008 DRAFT→PROPOSED→APPROVED→APPLIED, REJECTED terminal). audit_log infra (ADR-007 dedicated audit Postgres DB, INSERT-only role, hash chain, Kafka topic gmepay.audit.partner, lib-audit). Keycloak service (ADR-011 docker-compose Rocky 9, Postgres-backed); api-gateway becomes OAuth2 resource server; ops-partner-bff password=demo retired. Identity fields on partner: partner_code UNIQUE, legal_name_local, legal_name_romanized, tax_id + type discriminator (KR-BRN/KH-VAT/VN-MST/SG-UEN/generic), country_of_incorporation ISO-3166-α2, legal_form enum (CORP/LLC/MTO/EMI/BANK/OTHER), structured registered_address + operating_address, lei ISO-17442. Draft endpoints POST/PATCH/GET /v1/admin/partners/draft. RestConfigRegistryClient + admin-ui client.js updated. UI: wizard scaffold (8 tabs/stepper, server-side draft persistence per ADR-012), step-1 form with Yup regional validators, draft list with Resume button, Keycloak OIDC login replaces demo auth.</t>
+        </is>
+      </c>
+      <c r="F147" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t>Cross-cutting / Foundation</t>
+        </is>
+      </c>
+      <c r="H147" s="8" t="inlineStr">
+        <is>
+          <t>PARTNER_SETUP_PLAN.md §Slice 1; ADR-007/008/010/011/012/013</t>
+        </is>
+      </c>
+      <c r="I147" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J147" s="8" t="inlineStr">
+        <is>
+          <t>10.1, 8.2, 13.1, 13.2</t>
+        </is>
+      </c>
+      <c r="K147" s="8" t="inlineStr">
+        <is>
+          <t>Bitemporal partner aggregate + change_request FSM + audit_log + Keycloak; wizard step 1 live</t>
+        </is>
+      </c>
+      <c r="L147" s="8" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M147" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="N147" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q147" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R147" s="36" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S147" s="35" t="inlineStr">
+        <is>
+          <t>R0</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>21.2</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C148" s="8" t="inlineStr">
+        <is>
+          <t>21. Partner Setup re-baseline</t>
+        </is>
+      </c>
+      <c r="D148" s="8" t="inlineStr">
+        <is>
+          <t>Slice 2 — Contacts</t>
+        </is>
+      </c>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
+          <t>Wizard step 2 + 4-eyes machinery surfaced in UI. Backend: partner_contact child table (bitemporal) — id BIGSERIAL, partner_id FK, role enum (OPS_24X7/FINANCE/COMPLIANCE_MLRO/TECH/LEGAL/INCIDENT), name, email, phone_e164, is_authorized_signatory BOOL, notes. Reuse change_request from Slice 1. BFF: PATCH /v1/admin/partners/draft/{id}/step-2 (bulk replace), POST /v1/admin/partners/{id}/contacts (propose change), POST /v1/admin/partners/change-requests/{id}/approve. UI: multi-row contact editor with role dropdown + E.164 phone validation; generic Approval queue page (checker sees PROPOSED CRs, Approve/Reject with reason); read-only paginated audit log viewer on partner detail page.</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G148" s="8" t="inlineStr">
+        <is>
+          <t>Admin + BFF + config-registry</t>
+        </is>
+      </c>
+      <c r="H148" s="8" t="inlineStr">
+        <is>
+          <t>PARTNER_SETUP_PLAN.md §Slice 2; ADR-008</t>
+        </is>
+      </c>
+      <c r="I148" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="J148" s="8" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="K148" s="8" t="inlineStr">
+        <is>
+          <t>partner_contact entity + approval queue UI + audit log viewer</t>
+        </is>
+      </c>
+      <c r="L148" s="8" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M148" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="N148" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q148" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R148" s="36" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S148" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>21.3</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t>21. Partner Setup re-baseline</t>
+        </is>
+      </c>
+      <c r="D149" s="8" t="inlineStr">
+        <is>
+          <t>Slice 3 — KYB</t>
+        </is>
+      </c>
+      <c r="E149" s="8" t="inlineStr">
+        <is>
+          <t>Wizard step 3 + document vault + KYB screening adapter. Backend: MinIO bucket gmepay-partner-vault with object-lock compliance mode (ADR-006); lib-vault wraps MinIO SDK with virus-scan hook + Vault-key encryption. partner_document (bitemporal): id, partner_id FK, doc_type enum (LICENSE/CERT_INCORPORATION/AOA/BOARD_RESOLUTION/UBO_DECLARATION/FINANCIALS/CBDDQ/OTHER), vault_uri, version, expiry_date, verified_by, verified_at. partner_kyb (bitemporal): risk_rating (LOW/MEDIUM/HIGH), risk_rationale, next_review_date, license_type/number/authority/expiry, ubo_set_jsonb (array of {name, ownership_pct, is_pep, country}), wolfsberg_cbddq_doc_id FK. KybProvider port in lib-kyb (ADR-009). StubKybAdapter for internal dev; OctaKybAdapter lands when sandbox creds arrive. Kafka topic gmepay.kyb.screening, outbox-published same txn. New service services/kyb-adapter (Spring Boot module). UI: license details, UBO entry table (name + ownership% + PEP toggle + country), drag-drop document upload, Wolfsberg CBDDQ upload, Run screening button, document viewer modal with version history, screening result panel (latest result, decision history, rescreen).</t>
+        </is>
+      </c>
+      <c r="F149" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G149" s="8" t="inlineStr">
+        <is>
+          <t>KYB + Vault + Admin</t>
+        </is>
+      </c>
+      <c r="H149" s="8" t="inlineStr">
+        <is>
+          <t>PARTNER_SETUP_PLAN.md §Slice 3; ADR-006 (Vault), ADR-009 (KYB port)</t>
+        </is>
+      </c>
+      <c r="I149" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J149" s="8" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="K149" s="8" t="inlineStr">
+        <is>
+          <t>MinIO vault + lib-vault + kyb-adapter service + partner_document/partner_kyb tables + step-3 UI</t>
+        </is>
+      </c>
+      <c r="L149" s="8" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M149" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="N149" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q149" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R149" s="36" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S149" s="35" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C150" s="8" t="inlineStr">
+        <is>
+          <t>21. Partner Setup re-baseline</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t>Slice 4 — Banking &amp; Settlement</t>
+        </is>
+      </c>
+      <c r="E150" s="8" t="inlineStr">
+        <is>
+          <t>Wizard step 4 — settlement bank accounts, settlement cycle, methods, calendars. Backend: partner_bank_account (bitemporal) — id, partner_id FK, currency ISO-4217, bank_name, bic_swift, iban_or_account_number, account_holder_name, bank_country ISO-3166, intermediary_bic (opt), verification_status (UNVERIFIED/KFTC_VERIFIED/BANK_LETTER/MICRO_DEPOSIT), verification_evidence_doc_id FK, verification_date, is_primary BOOL, swift_charge_bearer (OUR/BEN/SHA), purpose (PAYOUT/FLOAT_TOPUP/REFUND). partner_settlement_config (bitemporal): partner_id PK, cycle_t_plus_n INT, cutoff_time, cutoff_timezone, settlement_method (SWIFT_MT103/KR_FIRM_BANKING/BAKONG/NAPAS_247/PROMPT_PAY/FAST_SG/OTHER). business_day_calendar seeded with Korean + ASEAN holidays go-live + 2 years (Chuseok, Tet, Songkran, Lunar New Year, etc.). KFTC 계좌실명조회 verification stub — port abstraction AccountVerificationProvider with KftcVerificationAdapter + StubVerificationAdapter. UI: bank account multi-row editor with per-row verification button, settlement config panel (cycle/cutoff/method/timezone picker), settlement preview ("with these settings, your Mon 11:30 KST txn pays out Wed 11:30 KST").</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t>Banking + Settlement</t>
+        </is>
+      </c>
+      <c r="H150" s="8" t="inlineStr">
+        <is>
+          <t>PARTNER_SETUP_PLAN.md §Slice 4; ADR-008; CAL-01 holiday calendars</t>
+        </is>
+      </c>
+      <c r="I150" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J150" s="8" t="inlineStr">
+        <is>
+          <t>21.2</t>
+        </is>
+      </c>
+      <c r="K150" s="8" t="inlineStr">
+        <is>
+          <t>partner_bank_account + partner_settlement_config + business_day_calendar + KFTC verification port + step-4 UI</t>
+        </is>
+      </c>
+      <c r="L150" s="8" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M150" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="N150" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q150" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R150" s="36" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S150" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>21.5</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C151" s="8" t="inlineStr">
+        <is>
+          <t>21. Partner Setup re-baseline</t>
+        </is>
+      </c>
+      <c r="D151" s="8" t="inlineStr">
+        <is>
+          <t>Slice 5 — Prefunding (OVERSEAS only)</t>
+        </is>
+      </c>
+      <c r="E151" s="8" t="inlineStr">
+        <is>
+          <t>Wizard step 5 + wire-up of existing PartnerBalanceEntity into partner-create txn. Backend: when partner is activated with funding_model=PREFUNDED or HYBRID, prefunding service creates balance row in same change_request. partner_prefunding_config (bitemporal): funding_model (PREFUNDED/POSTPAID/HYBRID), opening_balance_usd, low_balance_threshold_usd (default 10000), alert_tier_70/85/95_pct, credit_limit_usd (NULL=no limit), auto_suspend_on_breach BOOL, float_top_up_bank_account_id FK (purpose=FLOAT_TOPUP), top_up_reference_pattern VARCHAR (e.g. GMP-{partner_code}-{yyyyMMdd}), collateral_amount_usd (opt). Tier-alert generation: Kafka topic gmepay.prefunding.alert produced when balance crosses threshold; notification-webhook consumes. Auto-suspend: balance&lt;0 (or breach + auto_suspend_on_breach=true) publishes change_request(aggregate=partner, payload=status:SUSPENDED) with proposed_by=system — requires operator approval to lift. UI step 5 (OVERSEAS only): funding model radio, opening balance + ccy, threshold inputs with live preview, credit limit, top-up bank picker (filtered to FLOAT_TOPUP purpose), reference pattern preview. Prefunding dashboard tile on partner detail page: current balance, threshold gauge with tier coloring, recent top-ups, recent alerts.</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G151" s="8" t="inlineStr">
+        <is>
+          <t>Prefunding + Admin</t>
+        </is>
+      </c>
+      <c r="H151" s="8" t="inlineStr">
+        <is>
+          <t>PARTNER_SETUP_PLAN.md §Slice 5</t>
+        </is>
+      </c>
+      <c r="I151" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="J151" s="8" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="K151" s="8" t="inlineStr">
+        <is>
+          <t>partner_prefunding_config + PartnerBalanceEntity wired into create txn + tier alerts + auto-suspend + step-5 UI</t>
+        </is>
+      </c>
+      <c r="L151" s="8" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M151" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="N151" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q151" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R151" s="36" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S151" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C152" s="8" t="inlineStr">
+        <is>
+          <t>21. Partner Setup re-baseline</t>
+        </is>
+      </c>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t>Slice 6 — Commercial Terms</t>
+        </is>
+      </c>
+      <c r="E152" s="8" t="inlineStr">
+        <is>
+          <t>Wizard step 6 — financial-correctness slice (ccy split + rules + fees + FX + limits + contract). Backend: split settlement_currency into collection_ccy + settle_a_ccy (DAT-03 §4.3 + PRD-07 §5.3.2) via Expand/Backfill/Contract (ADR-013) across 3 releases. Rule persistence: today only POST /v1/rules/validate exists; add POST /v1/rules (create) + GET /v1/rules (list per partner) + PUT /v1/rules/{id} (update via change_request). Schema includes existing lib-domain Rule.validate "m_a + m_b ≥ 2%" invariant. partner_fee_schedule (bitemporal) per (partner × scheme × direction): fixed_fee, bps_fee, tier table (volume bands → bps). partner_fx_config (bitemporal): margin_bps, reference_rate_source (SEOUL_FX_BROKER/PARTNER_PROVIDED/MID_MARKET), quote_hold_seconds (default 300, range 60–1800). partner_limits (bitemporal): per_txn_min/max_usd, daily/monthly/annual_cap_usd. 소액해외송금업 hard-enforced server-side: per_txn ≤ 5000 USD, annual ≤ 50000 USD for that license type. partner_contract (bitemporal): effective_from/to, auto_renewal BOOL, notice_period_days, refund_chargeback_policy (PARTNER_BEARS/MERCHANT_BEARS/SHARED), termination_reason. transaction-mgmt + rate-fx updated to read new collection_ccy / settle_a_ccy split. UI step 6: split ccy picker, rule editor (multi-row per scheme/direction with margin sliders), fee schedule, FX margin slider + reference source + quote hold, limits with 소액해외송금업 visual cap markers, contract dates + auto-renewal toggle.</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G152" s="8" t="inlineStr">
+        <is>
+          <t>Pricing + FX + Limits + Contract</t>
+        </is>
+      </c>
+      <c r="H152" s="8" t="inlineStr">
+        <is>
+          <t>PARTNER_SETUP_PLAN.md §Slice 6; ADR-013 Expand/Backfill/Contract; DAT-03 §4.3; PRD-07 §5.3.2</t>
+        </is>
+      </c>
+      <c r="I152" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="J152" s="8" t="inlineStr">
+        <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="K152" s="8" t="inlineStr">
+        <is>
+          <t>collection_ccy/settle_a_ccy split + rule persistence + fee schedule + FX config + limits + contract + step-6 UI</t>
+        </is>
+      </c>
+      <c r="L152" s="8" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M152" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="N152" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q152" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R152" s="36" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S152" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>21. Partner Setup re-baseline</t>
+        </is>
+      </c>
+      <c r="D153" s="8" t="inlineStr">
+        <is>
+          <t>Slice 7 — Schemes &amp; Corridors</t>
+        </is>
+      </c>
+      <c r="E153" s="8" t="inlineStr">
+        <is>
+          <t>Wizard step 7 — scheme enablement + corridor matrix + per-partner scheme credentials. Backend: partner_scheme (bitemporal): partner_id, scheme_id, direction (INBOUND/OUTBOUND/BOTH), role (ACQUIRER/ISSUER/BOTH), zeropay_merchant_id, zeropay_sub_merchant_id, kftc_institution_code, partner_type_char (D/I — Zp0011 derivation). partner_corridor (bitemporal): partner_id, src_country, src_ccy, dst_country, dst_ccy, go_live_date, is_active. SchemeRouter rewrite from hardcoded KR→ZEROPAY to data-driven (reads partner_scheme join). Per-partner scheme credentials stored in Vault (ADR-006 pattern), referenced by partner_scheme.vault_secret_id. Approval method per (partner × scheme × payment_mode CPM/MPM): approval_method enum (CONFIRMATION/SILENT) — closes OI-01 / 1.2-T03. Operating hours per scheme (settlement cutoffs): seeded for ZeroPay (24×7 with KFTC 16:30 KST cutoff), Bakong (24×7 with NBC 09:00–15:00 ICT), etc. UI step 7: scheme enablement matrix (rows=schemes, columns=direction × role, checkboxes), per-row drill-down for ZeroPay specifics (merchantId, sub-merchantId, institution code, D/I, approval method per CPM/MPM), corridor matrix builder, operating hours preview.</t>
+        </is>
+      </c>
+      <c r="F153" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G153" s="8" t="inlineStr">
+        <is>
+          <t>Schemes + Corridors + Routing</t>
+        </is>
+      </c>
+      <c r="H153" s="8" t="inlineStr">
+        <is>
+          <t>PARTNER_SETUP_PLAN.md §Slice 7; ADR-006; OI-01</t>
+        </is>
+      </c>
+      <c r="I153" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J153" s="8" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="K153" s="8" t="inlineStr">
+        <is>
+          <t>partner_scheme + partner_corridor + data-driven SchemeRouter + Vault-stored creds + step-7 UI</t>
+        </is>
+      </c>
+      <c r="L153" s="8" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M153" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="N153" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q153" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R153" s="36" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S153" s="35" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>21.8</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C154" s="8" t="inlineStr">
+        <is>
+          <t>21. Partner Setup re-baseline</t>
+        </is>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
+        <is>
+          <t>Slice 8 — Credentials + Lifecycle + Reporting</t>
+        </is>
+      </c>
+      <c r="E154" s="8" t="inlineStr">
+        <is>
+          <t>Wizard step 8 — credential issuance + full FSM + regulatory reporting attributes. Backend: wire existing auth-identity/ApiKeyEntity + PrincipalEntity + notification-webhook/WebhookEndpointEntity into partner-create txn (the wire-up debt). Generate API key + HMAC secret on activation, return plaintext ONCE in response, store hash. IP allowlist: partner_ip_allowlist (up to 10 CIDRs); api-gateway pre-signature 403 enforcement. mTLS cert exchange: partner_mtls_cert (bitemporal) — cert_pem, fingerprint_sha256, expiry_date, status; mTLS verification at Nginx layer (ADR-002). Sandbox vs production credential pairs: partner_credential_environment enum (SANDBOX/PRODUCTION); sandbox prefix pk_test_/sk_test_. Credential rotation: scheduled job proposes rotation change_request at 11 months (12-month rotation per SEC-09); revoke endpoint with audit_log entry. Full FSM: Draft → KYB-Pending → KYB-Approved → Contract-Signed → Sandbox → UAT → Live → Suspended → Terminated. Transitions are change_request-gated; go-live + suspend require 4-eyes. Activation pre-condition gate: returns 422 + unmet[] until legal_name set, KYB approved, ≥1 verified bank account per settle_ccy, contracts signed, prefunding row created if OVERSEAS, ≥4 role contacts, ≥1 scheme enabled, sanctions clear or operator-overridden. Post-activation immutability: partner_code, country_of_incorporation, partner_type, collection_ccy, settle_a_ccy locked after first Live transition; mutations → 400 IMMUTABLE_AFTER_ACTIVATION. Suspension reason codes: LIMIT_BREACH/SANCTIONS_HIT/CREDENTIAL_COMPROMISE/KYB_LAPSED/CONTRACT_EXPIRED/OPERATOR_INITIATED. BOK 외환거래보고 attributes: bok_txn_code, bok_fx_reporting_category (INDIVIDUAL_AGGREGATE/INSTITUTIONAL), bok_remitter_type. Hometax e-tax-invoice: hometax_issuer_cert_id FK to vault doc, vat_treatment (ZERO_RATED_EXPORT/STANDARD/EXEMPT). KoFIU STR/CTR: kofiu_entity_id, ctr_threshold_krw (default 10,000,000), per-corridor STR enable flag. PIPA cross-border PII transfer notice: pipa_jurisdiction_allowlist[], legal_basis_code enum. Travel Rule (TRP/Sygna/IVMS101): travel_rule_protocol enum + endpoint config; ≥KRW 1M transfers must include IVMS101 originator + beneficiary block. UI step 8: Review tab (full summary with anchor jumps), Activate button (calls pre-condition gate, shows unmet[]), one-time credential modal (API key + HMAC + webhook signing secret, copy-to-clipboard, dismiss confirmation), confirmation operator stored secrets. Partner detail page (post-activation): status header with FSM menu, credential rotation panel, audit log full view, BOK/Hometax/KoFIU reporting settings tab, status-action menu (Suspend/Reactivate/Terminate with reason).</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G154" s="8" t="inlineStr">
+        <is>
+          <t>Credentials + FSM + Regulatory Reporting</t>
+        </is>
+      </c>
+      <c r="H154" s="8" t="inlineStr">
+        <is>
+          <t>PARTNER_SETUP_PLAN.md §Slice 8; ADR-002 (mTLS); ADR-008 (4-eyes); SEC-09 rotation</t>
+        </is>
+      </c>
+      <c r="I154" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="J154" s="8" t="inlineStr">
+        <is>
+          <t>21.5, 21.7</t>
+        </is>
+      </c>
+      <c r="K154" s="8" t="inlineStr">
+        <is>
+          <t>Credential issuance + full lifecycle FSM + activation gate + BOK/Hometax/KoFIU/PIPA/Travel-Rule reporting attrs + step-8 UI</t>
+        </is>
+      </c>
+      <c r="L154" s="8" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M154" s="35" t="n">
+        <v>40</v>
+      </c>
+      <c r="N154" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="35" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q154" s="35" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="R154" s="36" t="inlineStr">
+        <is>
+          <t>NOT STARTED</t>
+        </is>
+      </c>
+      <c r="S154" s="35" t="inlineStr">
+        <is>
+          <t>R3</t>
         </is>
       </c>
     </row>
